--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484261_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484261_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7464</v>
+        <v>2.2487</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0332</v>
+        <v>5.4265</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2867</v>
+        <v>-3.1778</v>
       </c>
       <c r="G2" t="n">
         <v>4.9167</v>
@@ -610,13 +610,13 @@
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3423</v>
+        <v>-0.1555</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8173</v>
+        <v>0.2106</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.475</v>
+        <v>-0.3661</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3405</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5439</v>
+        <v>1.5315</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3602</v>
+        <v>2.8884</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8163</v>
+        <v>-1.3568</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3138</v>
+        <v>0.8103</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3315</v>
+        <v>1.2556</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9822</v>
+        <v>-0.4453</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2542</v>
+        <v>2.9882</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2714</v>
+        <v>2.3536</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9828</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0595</v>
+        <v>-2.1779</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0601</v>
+        <v>-1.098</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.0799</v>
       </c>
       <c r="P3" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>0.898</v>
+        <v>-0.5289</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0594</v>
+        <v>-0.1464</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1613</v>
+        <v>-0.3825</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4959</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2519</v>
+        <v>1.2133</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2363</v>
+        <v>2.0568</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.8435</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2928</v>
+        <v>3.3138</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5971</v>
+        <v>1.3315</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8899</v>
+        <v>1.9822</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0519</v>
+        <v>3.2542</v>
       </c>
       <c r="K4" t="n">
-        <v>0.431</v>
+        <v>1.2714</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6208</v>
+        <v>1.9828</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7591</v>
+        <v>0.0595</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0281</v>
+        <v>0.0601</v>
       </c>
       <c r="O4" t="n">
-        <v>0.269</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5685</v>
+        <v>0.5675</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5519</v>
+        <v>0.756</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.1886</v>
       </c>
       <c r="V4" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" t="n">
-        <v>0.6093</v>
-      </c>
       <c r="X4" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1893</v>
+        <v>0.5053</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3828</v>
+        <v>1.3263</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1934</v>
+        <v>-0.821</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8103</v>
+        <v>0.2928</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2556</v>
+        <v>-0.5971</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4453</v>
+        <v>0.8899</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9882</v>
+        <v>1.0519</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3536</v>
+        <v>0.431</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6208</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1779</v>
+        <v>-0.7591</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.098</v>
+        <v>-1.0281</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0799</v>
+        <v>0.269</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8711</v>
+        <v>-0.1781</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.652</v>
+        <v>0.6419</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2191</v>
+        <v>-0.82</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5545</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4243</v>
+        <v>-1.3971</v>
       </c>
       <c r="E6" t="n">
         <v>-0.3419</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0824</v>
+        <v>-1.0551</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4444</v>
@@ -922,13 +922,13 @@
         <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.312</v>
+        <v>-0.2848</v>
       </c>
       <c r="T6" t="n">
         <v>0.3853</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6973</v>
+        <v>-0.67</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2772</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6402</v>
+        <v>-2.8659</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7661</v>
+        <v>-0.665</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8741</v>
+        <v>-2.2009</v>
       </c>
       <c r="G7" t="n">
         <v>-2.2202</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0339</v>
+        <v>0.8082</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3936</v>
+        <v>0.4947</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6403</v>
+        <v>0.3135</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0633</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9244</v>
+        <v>-3.7961</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8253</v>
+        <v>-0.7242</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0991</v>
+        <v>-3.0719</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8673</v>
@@ -1078,13 +1078,13 @@
         <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1772</v>
+        <v>-0.0488</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3247</v>
+        <v>0.4259</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5019</v>
+        <v>-0.4747</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1219</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.0365</v>
+        <v>-4.8264</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.746</v>
+        <v>-1.6449</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2905</v>
+        <v>-3.1815</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2902</v>
@@ -1156,13 +1156,13 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4253</v>
+        <v>-0.2153</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0221</v>
+        <v>0.1232</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4475</v>
+        <v>-0.3385</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3442</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.0269</v>
+        <v>-6.0818</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8698</v>
+        <v>-4.0609</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.157</v>
+        <v>-2.0209</v>
       </c>
       <c r="G10" t="n">
         <v>-6.6127</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.0151</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8335</v>
+        <v>-0.0246</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1267</v>
+        <v>0.0095</v>
       </c>
       <c r="V10" t="n">
         <v>0.1554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.273199999999999</v>
+        <v>-8.125400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4834</v>
+        <v>-4.2811</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7898</v>
+        <v>-3.8443</v>
       </c>
       <c r="G11" t="n">
         <v>-2.666</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2058</v>
+        <v>0.3535</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2849</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1231</v>
+        <v>0.0687</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4921</v>
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-21.594</v>
+        <v>-21.5939</v>
       </c>
       <c r="E12" t="n">
         <v>-0.01999999999999957</v>
@@ -1354,7 +1354,7 @@
         <v>-21.5737</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.767200000000001</v>
+        <v>-7.767199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-7.0902</v>
@@ -1369,7 +1369,7 @@
         <v>7.657900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>5.400700000000001</v>
+        <v>5.4007</v>
       </c>
       <c r="M12" t="n">
         <v>-20.8259</v>
@@ -1381,7 +1381,7 @@
         <v>-6.0777</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.813800000000001</v>
+        <v>-7.8138</v>
       </c>
       <c r="Q12" t="n">
         <v>-18.5576</v>
@@ -1390,13 +1390,13 @@
         <v>10.7439</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3026999999999999</v>
+        <v>0.3027</v>
       </c>
       <c r="T12" t="n">
-        <v>3.151400000000001</v>
+        <v>3.1515</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8488</v>
+        <v>-2.8487</v>
       </c>
       <c r="V12" t="n">
         <v>-6.3155</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.2972</v>
+        <v>8.4229</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6091</v>
+        <v>7.7102</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6881</v>
+        <v>0.7126</v>
       </c>
       <c r="G13" t="n">
         <v>4.1938</v>
@@ -1468,13 +1468,13 @@
         <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5023</v>
+        <v>0.628</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2642</v>
+        <v>0.3653</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2381</v>
+        <v>0.2626</v>
       </c>
       <c r="V13" t="n">
         <v>3.601</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3519</v>
+        <v>3.7179</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4728</v>
+        <v>2.884</v>
       </c>
       <c r="F14" t="n">
-        <v>1.879</v>
+        <v>0.8339</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3549</v>
+        <v>2.5077</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4357</v>
+        <v>3.2901</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08069999999999999</v>
+        <v>-0.7825</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1244</v>
+        <v>3.3366</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0435</v>
+        <v>3.8488</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0809</v>
+        <v>-0.5122</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4793</v>
+        <v>-0.8289</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4792</v>
+        <v>-0.5587</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0002</v>
+        <v>-0.2702</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9255</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.794</v>
+        <v>-0.3624</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1315</v>
+        <v>-0.1734</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>1.5507</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
         <v>0.6642</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4586</v>
+        <v>3.4211</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7</v>
+        <v>1.4617</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2414</v>
+        <v>1.9594</v>
       </c>
       <c r="G15" t="n">
-        <v>1.537</v>
+        <v>-0.3549</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9959</v>
+        <v>-0.4357</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4589</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5099</v>
+        <v>0.1244</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6196</v>
+        <v>0.0435</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8902</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9729</v>
+        <v>-0.4793</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6237</v>
+        <v>-0.4792</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3492</v>
+        <v>-0.0002</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2184</v>
+        <v>0.9947</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6124</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.394</v>
+        <v>0.2118</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="W15" t="n">
         <v>0.5545</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4431</v>
+        <v>3.1035</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5807</v>
+        <v>3.9922</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8624000000000001</v>
+        <v>-0.8887</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5077</v>
+        <v>1.537</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2901</v>
+        <v>1.9959</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7825</v>
+        <v>-0.4589</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3366</v>
+        <v>3.5099</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8488</v>
+        <v>2.6196</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5122</v>
+        <v>0.8902</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8289</v>
+        <v>-1.9729</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5587</v>
+        <v>-0.6237</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2702</v>
+        <v>-1.3492</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8106</v>
+        <v>0.8633</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6657</v>
+        <v>0.9046</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1448</v>
+        <v>-0.0413</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5507</v>
+        <v>-0.6642</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>0.5545</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0319</v>
+        <v>3.0499</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6149</v>
+        <v>2.2453</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.583</v>
+        <v>0.8046</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9264</v>
+        <v>0.2876</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1279</v>
+        <v>-0.3745</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2015</v>
+        <v>0.6621</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9092</v>
+        <v>2.0003</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7613</v>
+        <v>0.7982</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1478</v>
+        <v>1.2021</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9828</v>
+        <v>-1.7127</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6334</v>
+        <v>-1.1727</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3494</v>
+        <v>-0.5401</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1288</v>
+        <v>0.6136</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6824</v>
+        <v>0.4404</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5537</v>
+        <v>0.1732</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9196</v>
+        <v>1.8764</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0319</v>
+        <v>0.6555</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8877</v>
+        <v>1.2209</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2876</v>
+        <v>1.0536</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3745</v>
+        <v>0.042</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6621</v>
+        <v>1.0116</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0003</v>
+        <v>1.5481</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7982</v>
+        <v>0.2661</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2021</v>
+        <v>1.2821</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7127</v>
+        <v>-0.4945</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1727</v>
+        <v>-0.2241</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5401</v>
+        <v>-0.2704</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
         <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5167</v>
+        <v>-0.2126</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.773</v>
+        <v>-0.1931</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2563</v>
+        <v>-0.0194</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9128</v>
+        <v>1.6417</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5544</v>
+        <v>2.0082</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3584</v>
+        <v>-0.3665</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0536</v>
+        <v>0.9264</v>
       </c>
       <c r="H19" t="n">
-        <v>0.042</v>
+        <v>1.1279</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0116</v>
+        <v>-0.2015</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5481</v>
+        <v>2.9092</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2661</v>
+        <v>1.7613</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2821</v>
+        <v>1.1478</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4945</v>
+        <v>-1.9828</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2241</v>
+        <v>-0.6334</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2704</v>
+        <v>-1.3494</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1761</v>
+        <v>-0.2614</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2943</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1181</v>
+        <v>-0.3372</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8329</v>
+        <v>0.6178</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4862</v>
+        <v>1.0817</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6532</v>
+        <v>-0.4639</v>
       </c>
       <c r="G20" t="n">
         <v>0.7299</v>
@@ -2014,13 +2014,13 @@
         <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3803</v>
+        <v>0.1651</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6824</v>
+        <v>0.278</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3022</v>
+        <v>-0.1129</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0354</v>
+        <v>0.3187</v>
       </c>
       <c r="E21" t="n">
         <v>1.2132</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2486</v>
+        <v>-0.8945</v>
       </c>
       <c r="G21" t="n">
         <v>0.7054</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9828</v>
+        <v>-0.6287</v>
       </c>
       <c r="T21" t="n">
         <v>0.1294</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1122</v>
+        <v>-0.7581</v>
       </c>
       <c r="V21" t="n">
         <v>1.2186</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2263</v>
+        <v>-0.3214</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4836</v>
+        <v>-0.8769</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2573</v>
+        <v>0.5555</v>
       </c>
       <c r="G22" t="n">
         <v>-1.349</v>
@@ -2170,13 +2170,13 @@
         <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0493</v>
+        <v>-0.1444</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2805</v>
+        <v>0.3262</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7689</v>
+        <v>-0.4706</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3925</v>
+        <v>-2.9063</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4793</v>
+        <v>-2.0749</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9131</v>
+        <v>-0.8314</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4702</v>
@@ -2248,13 +2248,13 @@
         <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9222</v>
+        <v>-0.4361</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3026</v>
+        <v>0.1018</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6196</v>
+        <v>-0.5379</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.59380000000001</v>
+        <v>22.9422</v>
       </c>
       <c r="E24" t="n">
-        <v>20.3003</v>
+        <v>20.3002</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2936</v>
+        <v>2.6419</v>
       </c>
       <c r="G24" t="n">
         <v>7.767300000000001</v>
@@ -2317,7 +2317,7 @@
         <v>-5.400600000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>7.813700000000001</v>
+        <v>7.813699999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.7438</v>
@@ -2326,16 +2326,16 @@
         <v>18.5575</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3024000000000001</v>
+        <v>1.0457</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8487</v>
+        <v>2.8488</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.1514</v>
+        <v>-1.8032</v>
       </c>
       <c r="V24" t="n">
-        <v>6.315399999999999</v>
+        <v>6.3154</v>
       </c>
       <c r="W24" t="n">
         <v>7.3695</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484261_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484261_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3442</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-8.6432</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0499</v>
+        <v>1.8764</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2453</v>
+        <v>0.6555</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8046</v>
+        <v>1.2209</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2876</v>
+        <v>1.0536</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3745</v>
+        <v>0.042</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6621</v>
+        <v>1.0116</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0003</v>
+        <v>1.5481</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7982</v>
+        <v>0.2661</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2021</v>
+        <v>1.2821</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7127</v>
+        <v>-0.4945</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1727</v>
+        <v>-0.2241</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5401</v>
+        <v>-0.2704</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
         <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6136</v>
+        <v>-0.2126</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4404</v>
+        <v>-0.1931</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1732</v>
+        <v>-0.0194</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1894,72 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8764</v>
+        <v>1.8279</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6555</v>
+        <v>1.8279</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2209</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0536</v>
+        <v>1.8279</v>
       </c>
       <c r="H18" t="n">
-        <v>0.042</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0116</v>
+        <v>1.214</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5481</v>
+        <v>1.8279</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2661</v>
+        <v>0.614</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2821</v>
+        <v>1.214</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4945</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2241</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2704</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2126</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0194</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1953,11 +2039,16 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6178</v>
+        <v>1.222</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0817</v>
+        <v>0.4174</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4639</v>
+        <v>0.8046</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7299</v>
+        <v>-1.5404</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7439</v>
+        <v>-0.9885</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.014</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6985</v>
+        <v>0.1723</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5771</v>
+        <v>0.1842</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>-0.0118</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9686</v>
+        <v>-1.7127</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.1727</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>-0.5401</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1651</v>
+        <v>0.6136</v>
       </c>
       <c r="T20" t="n">
-        <v>0.278</v>
+        <v>0.4404</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1129</v>
+        <v>0.1732</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3187</v>
+        <v>0.6178</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2132</v>
+        <v>1.0817</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8945</v>
+        <v>-0.4639</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7054</v>
+        <v>0.7299</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2793</v>
+        <v>0.7439</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9848</v>
+        <v>-0.014</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0139</v>
+        <v>1.6985</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0844</v>
+        <v>1.5771</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9295</v>
+        <v>0.1214</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3085</v>
+        <v>-0.9686</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3638</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9447</v>
+        <v>-0.1354</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6287</v>
+        <v>0.1651</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1294</v>
+        <v>0.278</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7581</v>
+        <v>-0.1129</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3214</v>
+        <v>0.3187</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8769</v>
+        <v>1.2132</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5555</v>
+        <v>-0.8945</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.349</v>
+        <v>0.7054</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.2793</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2538</v>
+        <v>0.9848</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.031</v>
+        <v>2.0139</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0872</v>
+        <v>0.0844</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1182</v>
+        <v>1.9295</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.318</v>
+        <v>-1.3085</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1824</v>
+        <v>-0.3638</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1356</v>
+        <v>-0.9447</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.1721</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.1721</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.3441</v>
-      </c>
       <c r="S22" t="n">
-        <v>-0.1444</v>
+        <v>-0.6287</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3262</v>
+        <v>0.1294</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4706</v>
+        <v>-0.7581</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9063</v>
+        <v>-0.3214</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0749</v>
+        <v>-0.8769</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8314</v>
+        <v>0.5555</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4702</v>
+        <v>-1.349</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6613</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8089</v>
+        <v>-1.2538</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9814</v>
+        <v>-0.031</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6332</v>
+        <v>1.0872</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3482</v>
+        <v>-1.1182</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4889</v>
+        <v>-1.318</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0281</v>
+        <v>-1.1824</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5393</v>
+        <v>-0.1356</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4361</v>
+        <v>-0.1444</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1018</v>
+        <v>0.3262</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5379</v>
+        <v>-0.4706</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MACIAS MERINO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,152 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>22.9422</v>
+        <v>-2.9063</v>
       </c>
       <c r="E24" t="n">
-        <v>20.3002</v>
+        <v>-2.0749</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6419</v>
+        <v>-0.8314</v>
       </c>
       <c r="G24" t="n">
-        <v>7.767300000000001</v>
+        <v>-2.4702</v>
       </c>
       <c r="H24" t="n">
+        <v>-1.6613</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.8089</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.9814</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.6332</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.4889</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.0281</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.4361</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.5379</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484261_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>22.94219999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20.30020000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.641900000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7.767200000000001</v>
+      </c>
+      <c r="H25" t="n">
         <v>7.090100000000001</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>0.6772</v>
       </c>
-      <c r="J24" t="n">
-        <v>20.8258</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J25" t="n">
+        <v>20.8257</v>
+      </c>
+      <c r="K25" t="n">
         <v>14.748</v>
       </c>
-      <c r="L24" t="n">
-        <v>6.0777</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L25" t="n">
+        <v>6.0778</v>
+      </c>
+      <c r="M25" t="n">
         <v>-13.0585</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>-7.658000000000001</v>
       </c>
-      <c r="O24" t="n">
-        <v>-5.400600000000001</v>
-      </c>
-      <c r="P24" t="n">
-        <v>7.813699999999999</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="O25" t="n">
+        <v>-5.4006</v>
+      </c>
+      <c r="P25" t="n">
+        <v>7.813700000000001</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-10.7438</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>18.5575</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>1.0457</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>2.8488</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>-1.8032</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>6.3154</v>
       </c>
-      <c r="W24" t="n">
-        <v>7.3695</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="W25" t="n">
+        <v>7.369499999999999</v>
+      </c>
+      <c r="X25" t="n">
         <v>-1.054</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
